--- a/database/event/2635/event_2635_evp_summary.xlsx
+++ b/database/event/2635/event_2635_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1958</v>
+        <v>7.5875</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7239</v>
+        <v>3.9266</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4856</v>
+        <v>2.579</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1958</v>
+        <v>7.5875</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0591</v>
+        <v>1.4508</v>
       </c>
       <c r="G2" t="n">
         <v>6.1367</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0591</v>
+        <v>1.4508</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0591</v>
+        <v>1.4508</v>
       </c>
       <c r="J2" t="n">
         <v>6.1367</v>
@@ -529,7 +529,7 @@
         <v>212</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1958</v>
+        <v>7.5875</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4633</v>
+        <v>7.2756</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3448</v>
+        <v>3.7652</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.4547</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4633</v>
+        <v>7.2756</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0739</v>
+        <v>2.8862</v>
       </c>
       <c r="G3" t="n">
         <v>4.3894</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0739</v>
+        <v>2.8862</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0739</v>
+        <v>2.8862</v>
       </c>
       <c r="J3" t="n">
         <v>4.3894</v>
@@ -575,7 +575,7 @@
         <v>212</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4633</v>
+        <v>7.275600000000001</v>
       </c>
       <c r="N3" t="n">
         <v>342</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6816</v>
+        <v>5.9099</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9403</v>
+        <v>3.0584</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8739</v>
+        <v>1.9106</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6816</v>
+        <v>5.9099</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0597</v>
+        <v>1.2879</v>
       </c>
       <c r="G4" t="n">
         <v>4.622</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0597</v>
+        <v>1.2879</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0597</v>
+        <v>1.2879</v>
       </c>
       <c r="J4" t="n">
         <v>4.622</v>
@@ -621,7 +621,7 @@
         <v>212</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6817</v>
+        <v>5.9099</v>
       </c>
       <c r="N4" t="n">
         <v>342</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6113</v>
+        <v>5.757</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3864</v>
+        <v>2.9793</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4415</v>
+        <v>1.8497</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6113</v>
+        <v>5.757</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8602</v>
+        <v>4.006</v>
       </c>
       <c r="G5" t="n">
         <v>1.751</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8602</v>
+        <v>4.006</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8602</v>
+        <v>4.006</v>
       </c>
       <c r="J5" t="n">
         <v>1.751</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6112</v>
+        <v>5.757</v>
       </c>
       <c r="N5" t="n">
         <v>236</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9014</v>
+        <v>5.2314</v>
       </c>
       <c r="C6" t="n">
-        <v>2.019</v>
+        <v>2.7073</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1547</v>
+        <v>1.6403</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9014</v>
+        <v>5.2314</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6214</v>
+        <v>2.9514</v>
       </c>
       <c r="G6" t="n">
         <v>2.28</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6214</v>
+        <v>2.9514</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6214</v>
+        <v>2.9514</v>
       </c>
       <c r="J6" t="n">
         <v>2.28</v>
@@ -713,7 +713,7 @@
         <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9014</v>
+        <v>5.2314</v>
       </c>
       <c r="N6" t="n">
         <v>258</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8514</v>
+        <v>4.19</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9931</v>
+        <v>2.1684</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1345</v>
+        <v>1.2254</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8514</v>
+        <v>4.19</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3558</v>
+        <v>3.8521</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4956</v>
+        <v>0.3379</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3558</v>
+        <v>3.8521</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3558</v>
+        <v>3.8521</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4956</v>
+        <v>0.3379</v>
       </c>
       <c r="K7" t="n">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="L7" t="n">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8514</v>
+        <v>4.19</v>
       </c>
       <c r="N7" t="n">
-        <v>405</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5084</v>
+        <v>4.0139</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8156</v>
+        <v>2.0772</v>
       </c>
       <c r="D8" t="n">
-        <v>0.996</v>
+        <v>1.1552</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5084</v>
+        <v>4.0139</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7913</v>
+        <v>2.5183</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7171</v>
+        <v>1.4956</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7913</v>
+        <v>2.5183</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7913</v>
+        <v>2.5183</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7171</v>
+        <v>1.4956</v>
       </c>
       <c r="K8" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="L8" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5084</v>
+        <v>4.0139</v>
       </c>
       <c r="N8" t="n">
-        <v>342</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3312</v>
+        <v>3.9608</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7239</v>
+        <v>2.0498</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9244</v>
+        <v>1.1341</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3312</v>
+        <v>3.9608</v>
       </c>
       <c r="F9" t="n">
-        <v>2.036</v>
+        <v>3.2437</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2952</v>
+        <v>0.7171</v>
       </c>
       <c r="H9" t="n">
-        <v>2.036</v>
+        <v>3.2437</v>
       </c>
       <c r="I9" t="n">
-        <v>2.036</v>
+        <v>3.2437</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2952</v>
+        <v>0.7171</v>
       </c>
       <c r="K9" t="n">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="L9" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3312</v>
+        <v>3.9608</v>
       </c>
       <c r="N9" t="n">
-        <v>405</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9088</v>
+        <v>3.8305</v>
       </c>
       <c r="C10" t="n">
-        <v>1.5053</v>
+        <v>1.9823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7537</v>
+        <v>1.0822</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9088</v>
+        <v>3.8305</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3506</v>
+        <v>2.2723</v>
       </c>
       <c r="G10" t="n">
         <v>1.5582</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3506</v>
+        <v>2.2723</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3506</v>
+        <v>2.2723</v>
       </c>
       <c r="J10" t="n">
         <v>1.5582</v>
@@ -897,7 +897,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9088</v>
+        <v>3.8305</v>
       </c>
       <c r="N10" t="n">
         <v>258</v>
@@ -906,219 +906,219 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8863</v>
+        <v>3.7576</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4937</v>
+        <v>1.9446</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7446</v>
+        <v>1.0531</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8863</v>
+        <v>3.7576</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9497</v>
+        <v>3.016</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9366</v>
+        <v>0.7416</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9497</v>
+        <v>3.016</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9497</v>
+        <v>3.016</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9366</v>
+        <v>0.7416</v>
       </c>
       <c r="K11" t="n">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>217</v>
+        <v>65</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8863</v>
+        <v>3.7576</v>
       </c>
       <c r="N11" t="n">
-        <v>405</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.707</v>
+        <v>3.7558</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4009</v>
+        <v>1.9437</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6722</v>
+        <v>1.0524</v>
       </c>
       <c r="E12" t="n">
-        <v>2.707</v>
+        <v>3.7558</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3691</v>
+        <v>2.4606</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3379</v>
+        <v>1.2952</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3691</v>
+        <v>2.4606</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3691</v>
+        <v>2.4606</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3379</v>
+        <v>1.2952</v>
       </c>
       <c r="K12" t="n">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="L12" t="n">
-        <v>75</v>
+        <v>217</v>
       </c>
       <c r="M12" t="n">
-        <v>2.707</v>
+        <v>3.7558</v>
       </c>
       <c r="N12" t="n">
-        <v>151</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6741</v>
+        <v>3.2366</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3839</v>
+        <v>1.675</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6589</v>
+        <v>0.8456</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6741</v>
+        <v>3.2366</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9325</v>
+        <v>4.2366</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7416</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9325</v>
+        <v>4.34</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9325</v>
+        <v>4.34</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7416</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L13" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6741</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>162</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4653</v>
+        <v>3.016</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2758</v>
+        <v>1.5608</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5746</v>
+        <v>0.7577</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4653</v>
+        <v>3.016</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2795</v>
+        <v>3.016</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1858</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2795</v>
+        <v>3.016</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2795</v>
+        <v>3.016</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1858</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4653</v>
+        <v>3.016</v>
       </c>
       <c r="N14" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8843</v>
+        <v>2.8863</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9751</v>
+        <v>1.4937</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3399</v>
+        <v>0.706</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8843</v>
+        <v>2.8863</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3025</v>
+        <v>0.9497</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5818</v>
+        <v>1.9366</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3025</v>
+        <v>0.9497</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3025</v>
+        <v>0.9497</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5818</v>
+        <v>1.9366</v>
       </c>
       <c r="K15" t="n">
         <v>188</v>
@@ -1127,7 +1127,7 @@
         <v>217</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8843</v>
+        <v>2.8863</v>
       </c>
       <c r="N15" t="n">
         <v>405</v>
@@ -1136,369 +1136,369 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.778</v>
+        <v>2.5242</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9201</v>
+        <v>1.3063</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2969</v>
+        <v>0.5617</v>
       </c>
       <c r="E16" t="n">
-        <v>1.778</v>
+        <v>2.5242</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5809</v>
+        <v>1.3384</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1971</v>
+        <v>1.1858</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5809</v>
+        <v>1.3384</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5809</v>
+        <v>1.3384</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1971</v>
+        <v>1.1858</v>
       </c>
       <c r="K16" t="n">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="L16" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="M16" t="n">
-        <v>1.778</v>
+        <v>2.5242</v>
       </c>
       <c r="N16" t="n">
-        <v>236</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6995</v>
+        <v>2.1962</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8794999999999999</v>
+        <v>1.1366</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2652</v>
+        <v>0.4311</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6995</v>
+        <v>2.1962</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6995</v>
+        <v>1.9433</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2529</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6995</v>
+        <v>1.9433</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6995</v>
+        <v>1.9433</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2529</v>
       </c>
       <c r="K17" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6995</v>
+        <v>2.1962</v>
       </c>
       <c r="N17" t="n">
-        <v>118</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5837</v>
+        <v>2.1562</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8196</v>
+        <v>1.1159</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2184</v>
+        <v>0.4151</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5837</v>
+        <v>2.1562</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3308</v>
+        <v>2.1562</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2529</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3308</v>
+        <v>2.1562</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3308</v>
+        <v>2.1562</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2529</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="L18" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5837</v>
+        <v>2.1562</v>
       </c>
       <c r="N18" t="n">
-        <v>171</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5383</v>
+        <v>2.1023</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7961</v>
+        <v>1.088</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2001</v>
+        <v>0.3936</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5383</v>
+        <v>2.1023</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6351</v>
+        <v>0.9052</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0968</v>
+        <v>1.1971</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6351</v>
+        <v>0.9052</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6351</v>
+        <v>0.9052</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0968</v>
+        <v>1.1971</v>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="L19" t="n">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5383</v>
+        <v>2.1023</v>
       </c>
       <c r="N19" t="n">
-        <v>171</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5119</v>
+        <v>2.0941</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7824</v>
+        <v>1.0837</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1894</v>
+        <v>0.3904</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5119</v>
+        <v>2.0941</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5119</v>
+        <v>0.307</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.7871</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5119</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5119</v>
+        <v>0.307</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.7871</v>
       </c>
       <c r="K20" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5119</v>
+        <v>2.0941</v>
       </c>
       <c r="N20" t="n">
-        <v>107</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5072</v>
+        <v>1.9036</v>
       </c>
       <c r="C21" t="n">
-        <v>0.78</v>
+        <v>0.9851</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1875</v>
+        <v>0.3145</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5072</v>
+        <v>1.9036</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5072</v>
+        <v>1.633</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.2706</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5072</v>
+        <v>1.633</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5072</v>
+        <v>1.633</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.2706</v>
       </c>
       <c r="K21" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5072</v>
+        <v>1.9036</v>
       </c>
       <c r="N21" t="n">
-        <v>143</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4996</v>
+        <v>1.8843</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7761</v>
+        <v>0.9751</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1844</v>
+        <v>0.3068</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4996</v>
+        <v>1.8843</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1684</v>
+        <v>0.3025</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3312</v>
+        <v>1.5818</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1684</v>
+        <v>0.3025</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1684</v>
+        <v>0.3025</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3312</v>
+        <v>1.5818</v>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="L22" t="n">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4996</v>
+        <v>1.8843</v>
       </c>
       <c r="N22" t="n">
-        <v>171</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4559</v>
+        <v>1.8424</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7534</v>
+        <v>0.9535</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1668</v>
+        <v>0.2901</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4559</v>
+        <v>1.8424</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4559</v>
+        <v>1.8424</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4559</v>
+        <v>1.8424</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4559</v>
+        <v>1.8424</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="L23" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4559</v>
+        <v>1.8424</v>
       </c>
       <c r="N23" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4485</v>
+        <v>1.7375</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7496</v>
+        <v>0.8992</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1638</v>
+        <v>0.2483</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4485</v>
+        <v>1.7375</v>
       </c>
       <c r="F24" t="n">
-        <v>0.669</v>
+        <v>0.958</v>
       </c>
       <c r="G24" t="n">
         <v>0.7795</v>
       </c>
       <c r="H24" t="n">
-        <v>0.669</v>
+        <v>0.958</v>
       </c>
       <c r="I24" t="n">
-        <v>0.669</v>
+        <v>0.958</v>
       </c>
       <c r="J24" t="n">
         <v>0.7795</v>
@@ -1541,7 +1541,7 @@
         <v>101</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4485</v>
+        <v>1.7375</v>
       </c>
       <c r="N24" t="n">
         <v>236</v>
@@ -1550,553 +1550,553 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4361</v>
+        <v>1.7152</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7432</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1588</v>
+        <v>0.2394</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4361</v>
+        <v>1.7152</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.351</v>
+        <v>1.4733</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7871</v>
+        <v>0.2419</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.351</v>
+        <v>1.4733</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.351</v>
+        <v>1.4733</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7871</v>
+        <v>0.2419</v>
       </c>
       <c r="K25" t="n">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="L25" t="n">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4361</v>
+        <v>1.7152</v>
       </c>
       <c r="N25" t="n">
-        <v>236</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3988</v>
+        <v>1.6963</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7239</v>
+        <v>0.8779</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1437</v>
+        <v>0.2319</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3988</v>
+        <v>1.6963</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1569</v>
+        <v>1.6963</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2419</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1569</v>
+        <v>1.6963</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1569</v>
+        <v>1.6963</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2419</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L26" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3988</v>
+        <v>1.6963</v>
       </c>
       <c r="N26" t="n">
-        <v>162</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.374</v>
+        <v>1.568</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7111</v>
+        <v>0.8115</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1337</v>
+        <v>0.1808</v>
       </c>
       <c r="E27" t="n">
-        <v>1.374</v>
+        <v>1.568</v>
       </c>
       <c r="F27" t="n">
-        <v>1.374</v>
+        <v>0.9744</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.5936</v>
       </c>
       <c r="H27" t="n">
-        <v>1.374</v>
+        <v>0.9744</v>
       </c>
       <c r="I27" t="n">
-        <v>1.374</v>
+        <v>0.9744</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.5936</v>
       </c>
       <c r="K27" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>1.374</v>
+        <v>1.568</v>
       </c>
       <c r="N27" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1185</v>
+        <v>1.5659</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5788</v>
+        <v>0.8104</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0305</v>
+        <v>0.1799</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1185</v>
+        <v>1.5659</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1185</v>
+        <v>1.6627</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.0968</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1185</v>
+        <v>1.6627</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1185</v>
+        <v>1.6627</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.0968</v>
       </c>
       <c r="K28" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1185</v>
+        <v>1.5659</v>
       </c>
       <c r="N28" t="n">
-        <v>126</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.087</v>
+        <v>1.4996</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5625</v>
+        <v>0.7761</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0178</v>
+        <v>0.1535</v>
       </c>
       <c r="E29" t="n">
-        <v>1.087</v>
+        <v>1.4996</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4934</v>
+        <v>1.1684</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5936</v>
+        <v>0.3312</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4934</v>
+        <v>1.1684</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4934</v>
+        <v>1.1684</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5936</v>
+        <v>0.3312</v>
       </c>
       <c r="K29" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L29" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="M29" t="n">
-        <v>1.087</v>
+        <v>1.4996</v>
       </c>
       <c r="N29" t="n">
-        <v>124</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0847</v>
+        <v>1.4472</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5613</v>
+        <v>0.7489</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0168</v>
+        <v>0.1327</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0847</v>
+        <v>1.4472</v>
       </c>
       <c r="F30" t="n">
-        <v>1.9582</v>
+        <v>1.4472</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.9582</v>
+        <v>1.4472</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9582</v>
+        <v>1.4472</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0847</v>
+        <v>1.4472</v>
       </c>
       <c r="N30" t="n">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0626</v>
+        <v>1.3365</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.6917</v>
       </c>
       <c r="D31" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0886</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0626</v>
+        <v>1.3365</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0626</v>
+        <v>1.3365</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0626</v>
+        <v>1.3365</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0626</v>
+        <v>1.3365</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0626</v>
+        <v>1.3365</v>
       </c>
       <c r="N31" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9546</v>
+        <v>1.2862</v>
       </c>
       <c r="C32" t="n">
-        <v>0.494</v>
+        <v>0.6656</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0357</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9546</v>
+        <v>1.2862</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9546</v>
+        <v>2.1597</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9546</v>
+        <v>2.1597</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9546</v>
+        <v>2.1597</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9546</v>
+        <v>1.2862</v>
       </c>
       <c r="N32" t="n">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9223</v>
+        <v>1.168</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4773</v>
+        <v>0.6045</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0488</v>
+        <v>0.0214</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9223</v>
+        <v>1.168</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9223</v>
+        <v>1.168</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9223</v>
+        <v>1.168</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9223</v>
+        <v>1.168</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9223</v>
+        <v>1.168</v>
       </c>
       <c r="N33" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9084</v>
+        <v>1.0405</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4701</v>
+        <v>0.5385</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0544</v>
+        <v>-0.0294</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9084</v>
+        <v>1.0405</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6378</v>
+        <v>1.1017</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2706</v>
+        <v>-0.0612</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6378</v>
+        <v>1.1017</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6378</v>
+        <v>1.1017</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2706</v>
+        <v>-0.0612</v>
       </c>
       <c r="K34" t="n">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="L34" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9084000000000001</v>
+        <v>1.0405</v>
       </c>
       <c r="N34" t="n">
-        <v>258</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8474</v>
+        <v>1.0403</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4385</v>
+        <v>0.5384</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.079</v>
+        <v>-0.0295</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8474</v>
+        <v>1.0403</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8474</v>
+        <v>1.0403</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8474</v>
+        <v>1.0403</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8474</v>
+        <v>1.0403</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="L35" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8473999999999999</v>
+        <v>1.0403</v>
       </c>
       <c r="N35" t="n">
-        <v>151</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8292</v>
+        <v>1.0058</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4291</v>
+        <v>0.5205</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0864</v>
+        <v>-0.0432</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8292</v>
+        <v>1.0058</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8292</v>
+        <v>1.0058</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8292</v>
+        <v>1.0058</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8292</v>
+        <v>1.0058</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8292</v>
+        <v>1.0058</v>
       </c>
       <c r="N36" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6422</v>
+        <v>0.9852</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3323</v>
+        <v>0.5099</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1619</v>
+        <v>-0.0514</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6422</v>
+        <v>0.9852</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.967</v>
+        <v>-0.624</v>
       </c>
       <c r="G37" t="n">
         <v>1.6092</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.967</v>
+        <v>-0.624</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.967</v>
+        <v>-0.624</v>
       </c>
       <c r="J37" t="n">
         <v>1.6092</v>
@@ -2139,7 +2139,7 @@
         <v>212</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6422</v>
+        <v>0.9852</v>
       </c>
       <c r="N37" t="n">
         <v>342</v>
@@ -2148,216 +2148,216 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6181</v>
+        <v>0.9596</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3199</v>
+        <v>0.4966</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1717</v>
+        <v>-0.0616</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6181</v>
+        <v>0.9596</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9887</v>
+        <v>1.9596</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.3706</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9887</v>
+        <v>1.9596</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9887</v>
+        <v>1.9596</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3706</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="L38" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6181000000000001</v>
+        <v>0.9596</v>
       </c>
       <c r="N38" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5271</v>
+        <v>0.8292</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2728</v>
+        <v>0.4291</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2084</v>
+        <v>-0.1136</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5271</v>
+        <v>0.8292</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5271</v>
+        <v>0.8292</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5271</v>
+        <v>0.8292</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5271</v>
+        <v>0.8292</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5271</v>
+        <v>0.8292</v>
       </c>
       <c r="N39" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.7573</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2611</v>
+        <v>0.3919</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2176</v>
+        <v>-0.1422</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.7573</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5657</v>
+        <v>0.2044</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0612</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5657</v>
+        <v>0.2044</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5657</v>
+        <v>0.2044</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0612</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="L40" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.7573</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4332</v>
+        <v>0.7076</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2242</v>
+        <v>0.3662</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2464</v>
+        <v>-0.162</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4332</v>
+        <v>0.7076</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4332</v>
+        <v>1.0782</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4332</v>
+        <v>1.0782</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4332</v>
+        <v>1.0782</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="K41" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4332</v>
+        <v>0.7076</v>
       </c>
       <c r="N41" t="n">
-        <v>118</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4297</v>
+        <v>0.7075</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2224</v>
+        <v>0.3661</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2478</v>
+        <v>-0.162</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4297</v>
+        <v>0.7075</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4297</v>
+        <v>0.7075</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4297</v>
+        <v>0.7075</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4297</v>
+        <v>0.7075</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4297</v>
+        <v>0.7075</v>
       </c>
       <c r="N42" t="n">
         <v>118</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2417</v>
+        <v>0.6437</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1251</v>
+        <v>0.3331</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3237</v>
+        <v>-0.1875</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2417</v>
+        <v>0.6437</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2417</v>
+        <v>0.6437</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2417</v>
+        <v>0.6437</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2417</v>
+        <v>0.6437</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2417</v>
+        <v>0.6437</v>
       </c>
       <c r="N43" t="n">
         <v>143</v>
@@ -2424,308 +2424,308 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1499</v>
+        <v>0.5271</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0776</v>
+        <v>0.2728</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3608</v>
+        <v>-0.2339</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1499</v>
+        <v>0.5271</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.403</v>
+        <v>0.5271</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5528999999999999</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.403</v>
+        <v>0.5271</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.403</v>
+        <v>0.5271</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5528999999999999</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L44" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1498999999999999</v>
+        <v>0.5271</v>
       </c>
       <c r="N44" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1222</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.372</v>
+        <v>-0.2361</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1222</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0955</v>
+        <v>1.4705</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.9488</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0955</v>
+        <v>1.4705</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0955</v>
+        <v>1.4705</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.9488</v>
       </c>
       <c r="K45" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L45" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1221999999999999</v>
+        <v>0.5216999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.098</v>
+        <v>0.4732</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0507</v>
+        <v>0.2449</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3818</v>
+        <v>-0.2554</v>
       </c>
       <c r="E46" t="n">
-        <v>0.098</v>
+        <v>0.4732</v>
       </c>
       <c r="F46" t="n">
-        <v>0.098</v>
+        <v>1.4465</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.098</v>
+        <v>1.4465</v>
       </c>
       <c r="I46" t="n">
-        <v>0.098</v>
+        <v>1.4465</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M46" t="n">
-        <v>0.098</v>
+        <v>0.4731999999999998</v>
       </c>
       <c r="N46" t="n">
-        <v>99</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0975</v>
+        <v>0.4113</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0505</v>
+        <v>0.2129</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.382</v>
+        <v>-0.28</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0975</v>
+        <v>0.4113</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0975</v>
+        <v>0.4113</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0975</v>
+        <v>0.4113</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0975</v>
+        <v>0.4113</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.0975</v>
+        <v>0.4113</v>
       </c>
       <c r="N47" t="n">
-        <v>143</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.3914</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0483</v>
+        <v>0.2026</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3837</v>
+        <v>-0.288</v>
       </c>
       <c r="E48" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.3914</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0421</v>
+        <v>0.3914</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.9488</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.0421</v>
+        <v>0.3914</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0421</v>
+        <v>0.3914</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9488</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="L48" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.09330000000000005</v>
+        <v>0.3914</v>
       </c>
       <c r="N48" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2019</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0043</v>
+        <v>0.1045</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4248</v>
+        <v>-0.3635</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2019</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8035</v>
+        <v>0.2019</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.8119</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8035</v>
+        <v>0.2019</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8035</v>
+        <v>0.2019</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8119</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="L49" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.008399999999999963</v>
+        <v>0.2019</v>
       </c>
       <c r="N49" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1368</v>
+        <v>0.103</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0708</v>
+        <v>0.0533</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4766</v>
+        <v>-0.4029</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1368</v>
+        <v>0.103</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1368</v>
+        <v>0.103</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1368</v>
+        <v>0.103</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1368</v>
+        <v>0.103</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1368</v>
+        <v>0.103</v>
       </c>
       <c r="N50" t="n">
         <v>99</v>
@@ -2746,599 +2746,599 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1442</v>
+        <v>0.015</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0746</v>
+        <v>0.0078</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4796</v>
+        <v>-0.4379</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1442</v>
+        <v>0.015</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1442</v>
+        <v>0.8269</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.8119</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1442</v>
+        <v>0.8269</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1442</v>
+        <v>0.8269</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.8119</v>
       </c>
       <c r="K51" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1442</v>
+        <v>0.01500000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1368</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0825</v>
+        <v>-0.0708</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4858</v>
+        <v>-0.4984</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1368</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1368</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1368</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1368</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1594</v>
+        <v>-0.1368</v>
       </c>
       <c r="N52" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1728</v>
+        <v>-0.1442</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0746</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4912</v>
+        <v>-0.5014</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1728</v>
+        <v>-0.1442</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1728</v>
+        <v>-0.1442</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1728</v>
+        <v>-0.1442</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1728</v>
+        <v>-0.1442</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1728</v>
+        <v>-0.1442</v>
       </c>
       <c r="N53" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1594</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.092</v>
+        <v>-0.0825</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4931</v>
+        <v>-0.5074</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1594</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1594</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1594</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1594</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1777</v>
+        <v>-0.1594</v>
       </c>
       <c r="N54" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.252</v>
+        <v>-0.1777</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1304</v>
+        <v>-0.092</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5232</v>
+        <v>-0.5147</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.252</v>
+        <v>-0.1777</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.252</v>
+        <v>-0.1777</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.252</v>
+        <v>-0.1777</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.252</v>
+        <v>-0.1777</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.252</v>
+        <v>-0.1777</v>
       </c>
       <c r="N55" t="n">
-        <v>112</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2656</v>
+        <v>-0.252</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1375</v>
+        <v>-0.1304</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5443</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2656</v>
+        <v>-0.252</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2656</v>
+        <v>-0.252</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2656</v>
+        <v>-0.252</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2656</v>
+        <v>-0.252</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2656</v>
+        <v>-0.252</v>
       </c>
       <c r="N56" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.397</v>
+        <v>-0.2656</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2055</v>
+        <v>-0.1375</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5817</v>
+        <v>-0.5497</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.397</v>
+        <v>-0.2656</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.397</v>
+        <v>-0.2656</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.397</v>
+        <v>-0.2656</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.397</v>
+        <v>-0.2656</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.397</v>
+        <v>-0.2656</v>
       </c>
       <c r="N57" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5019</v>
+        <v>-0.3277</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2597</v>
+        <v>-0.1696</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6241</v>
+        <v>-0.5745</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5019</v>
+        <v>-0.3277</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5019</v>
+        <v>0.6723</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5019</v>
+        <v>0.6723</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5019</v>
+        <v>0.6723</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K58" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5019</v>
+        <v>-0.3277</v>
       </c>
       <c r="N58" t="n">
-        <v>78</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5246</v>
+        <v>-0.3297</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2715</v>
+        <v>-0.1706</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6333</v>
+        <v>-0.5753</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5246</v>
+        <v>-0.3297</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4754</v>
+        <v>0.6</v>
       </c>
       <c r="G59" t="n">
-        <v>-1</v>
+        <v>-0.9297</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4754</v>
+        <v>0.6</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4754</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
-        <v>-1</v>
+        <v>-0.9297</v>
       </c>
       <c r="K59" t="n">
         <v>97</v>
       </c>
       <c r="L59" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5246</v>
+        <v>-0.3297</v>
       </c>
       <c r="N59" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>ngiN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5448</v>
+        <v>-0.3453</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2819</v>
+        <v>-0.1787</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6414</v>
+        <v>-0.5815</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5448</v>
+        <v>-0.3453</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3849</v>
+        <v>-0.3453</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.9297</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3849</v>
+        <v>-0.3453</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3849</v>
+        <v>-0.3453</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.9297</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L60" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5448</v>
+        <v>-0.3453</v>
       </c>
       <c r="N60" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ngiN</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2908</v>
+        <v>-0.2055</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6484</v>
+        <v>-0.6021</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.397</v>
       </c>
       <c r="N61" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6111</v>
+        <v>-0.423</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3162</v>
+        <v>-0.2189</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6682</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6111</v>
+        <v>-0.423</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6111</v>
+        <v>-0.423</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6111</v>
+        <v>-0.423</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6111</v>
+        <v>-0.423</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6111</v>
+        <v>-0.423</v>
       </c>
       <c r="N62" t="n">
-        <v>78</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6253</v>
+        <v>-0.5019</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3236</v>
+        <v>-0.2597</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.674</v>
+        <v>-0.6439</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6253</v>
+        <v>-0.5019</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6253</v>
+        <v>-0.5019</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6253</v>
+        <v>-0.5019</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6253</v>
+        <v>-0.5019</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6253</v>
+        <v>-0.5019</v>
       </c>
       <c r="N63" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6896</v>
+        <v>-0.5834</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3569</v>
+        <v>-0.3019</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6999</v>
+        <v>-0.6763</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6896</v>
+        <v>-0.5834</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4688</v>
+        <v>-0.3626</v>
       </c>
       <c r="G64" t="n">
         <v>-0.2208</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4688</v>
+        <v>-0.3626</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4688</v>
+        <v>-0.3626</v>
       </c>
       <c r="J64" t="n">
         <v>-0.2208</v>
@@ -3381,7 +3381,7 @@
         <v>65</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6896</v>
+        <v>-0.5833999999999999</v>
       </c>
       <c r="N64" t="n">
         <v>162</v>
@@ -3390,323 +3390,323 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6958</v>
+        <v>-0.6111</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3601</v>
+        <v>-0.3162</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7025</v>
+        <v>-0.6874</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6958</v>
+        <v>-0.6111</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.6958</v>
+        <v>-0.6111</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6958</v>
+        <v>-0.6111</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.6958</v>
+        <v>-0.6111</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6958</v>
+        <v>-0.6111</v>
       </c>
       <c r="N65" t="n">
-        <v>118</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8819</v>
+        <v>-0.6173</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4564</v>
+        <v>-0.3195</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7776</v>
+        <v>-0.6898</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8819</v>
+        <v>-0.6173</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8819</v>
+        <v>-0.6173</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8819</v>
+        <v>-0.6173</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8819</v>
+        <v>-0.6173</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8819</v>
+        <v>-0.6173</v>
       </c>
       <c r="N66" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8981</v>
+        <v>-0.6378</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4648</v>
+        <v>-0.3301</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7842</v>
+        <v>-0.698</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8981</v>
+        <v>-0.6378</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8981</v>
+        <v>-0.5356</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-0.1022</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8981</v>
+        <v>-0.5356</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8981</v>
+        <v>-0.5356</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-0.1022</v>
       </c>
       <c r="K67" t="n">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8981</v>
+        <v>-0.6377999999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>107</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9026</v>
+        <v>-0.8262</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4671</v>
+        <v>-0.4276</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.786</v>
+        <v>-0.7731</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9026</v>
+        <v>-0.8262</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9026</v>
+        <v>-0.8262</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9026</v>
+        <v>-0.8262</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.9026</v>
+        <v>-0.8262</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9026</v>
+        <v>-0.8262</v>
       </c>
       <c r="N68" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9187</v>
+        <v>-0.8819</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4754</v>
+        <v>-0.4564</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7925</v>
+        <v>-0.7953</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9187</v>
+        <v>-0.8819</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8165</v>
+        <v>-0.8819</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.1022</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8165</v>
+        <v>-0.8819</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8165</v>
+        <v>-0.8819</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.1022</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="L69" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9187</v>
+        <v>-0.8819</v>
       </c>
       <c r="N69" t="n">
-        <v>258</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0525</v>
+        <v>-0.9026</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5447</v>
+        <v>-0.4671</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8465</v>
+        <v>-0.8035</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0525</v>
+        <v>-0.9026</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0525</v>
+        <v>-0.9026</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0525</v>
+        <v>-0.9026</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.0525</v>
+        <v>-0.9026</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0525</v>
+        <v>-0.9026</v>
       </c>
       <c r="N70" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.11</v>
+        <v>-1.0525</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5744</v>
+        <v>-0.5447</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8698</v>
+        <v>-0.8632</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.11</v>
+        <v>-1.0525</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.11</v>
+        <v>-1.0525</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.11</v>
+        <v>-1.0525</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.11</v>
+        <v>-1.0525</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.11</v>
+        <v>-1.0525</v>
       </c>
       <c r="N71" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72">
@@ -3722,7 +3722,7 @@
         <v>-0.5993000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8892</v>
+        <v>-0.9053</v>
       </c>
       <c r="E72" t="n">
         <v>-1.158</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2869</v>
+        <v>-1.2063</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.666</v>
+        <v>-0.6243</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9412</v>
+        <v>-0.9245</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2869</v>
+        <v>-1.2063</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2869</v>
+        <v>-1.2063</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2869</v>
+        <v>-1.2063</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2869</v>
+        <v>-1.2063</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.2869</v>
+        <v>-1.2063</v>
       </c>
       <c r="N73" t="n">
         <v>143</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6820000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9537</v>
+        <v>-0.9689</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3178</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7615</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0158</v>
+        <v>-1.0301</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4714</v>
@@ -3896,231 +3896,231 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.515</v>
+        <v>-1.5044</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.784</v>
+        <v>-0.7785</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0334</v>
+        <v>-1.0433</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.515</v>
+        <v>-1.5044</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.515</v>
+        <v>0.0538</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-1.5582</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.515</v>
+        <v>0.0538</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.515</v>
+        <v>0.0538</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-1.5582</v>
       </c>
       <c r="K76" t="n">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.515</v>
+        <v>-1.5044</v>
       </c>
       <c r="N76" t="n">
-        <v>143</v>
+        <v>405</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5335</v>
+        <v>-1.515</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7936</v>
+        <v>-0.784</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0409</v>
+        <v>-1.0475</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5335</v>
+        <v>-1.515</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5335</v>
+        <v>-1.515</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5335</v>
+        <v>-1.515</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.5335</v>
+        <v>-1.515</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.5335</v>
+        <v>-1.515</v>
       </c>
       <c r="N77" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.7925</v>
+        <v>-1.5335</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.9276</v>
+        <v>-0.7936</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1455</v>
+        <v>-1.0549</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.7925</v>
+        <v>-1.5335</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7925</v>
+        <v>-1.5335</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.7925</v>
+        <v>-1.5335</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.7925</v>
+        <v>-1.5335</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.7925</v>
+        <v>-1.5335</v>
       </c>
       <c r="N78" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.8526</v>
+        <v>-1.7925</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.9587</v>
+        <v>-0.9276</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1698</v>
+        <v>-1.158</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.8526</v>
+        <v>-1.7925</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.2546</v>
+        <v>-1.7925</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.598</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.2546</v>
+        <v>-1.7925</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2546</v>
+        <v>-1.7925</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.598</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="L79" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.8526</v>
+        <v>-1.7925</v>
       </c>
       <c r="N79" t="n">
-        <v>258</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.975</v>
+        <v>-1.8523</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.0221</v>
+        <v>-0.9586</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2192</v>
+        <v>-1.1819</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.975</v>
+        <v>-1.8523</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.4168</v>
+        <v>-1.2543</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.5582</v>
+        <v>-0.598</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.4168</v>
+        <v>-1.2543</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4168</v>
+        <v>-1.2543</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.5582</v>
+        <v>-0.598</v>
       </c>
       <c r="K80" t="n">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="L80" t="n">
-        <v>217</v>
+        <v>124</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.975</v>
+        <v>-1.8523</v>
       </c>
       <c r="N80" t="n">
-        <v>405</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81">
@@ -4136,7 +4136,7 @@
         <v>-1.0489</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2402</v>
+        <v>-1.2514</v>
       </c>
       <c r="E81" t="n">
         <v>-2.0269</v>
